--- a/tool/cmd/gen-go-db/test.xlsx
+++ b/tool/cmd/gen-go-db/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8724"/>
   </bookViews>
   <sheets>
     <sheet name="tm_teacher" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="161">
   <si>
     <t>列名</t>
   </si>
@@ -84,6 +84,15 @@
     <t>card_no</t>
   </si>
   <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
     <t>jpa_version</t>
   </si>
   <si>
@@ -121,6 +130,12 @@
   </si>
   <si>
     <t>tm_teacher_phone_IDX</t>
+  </si>
+  <si>
+    <t>tm_teacher_classid_IDX</t>
+  </si>
+  <si>
+    <t>tm_teacher_Name_IDX</t>
   </si>
   <si>
     <t>自定义脚本名字</t>
@@ -1554,10 +1569,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="27" style="14" customWidth="1"/>
     <col min="2" max="2" width="16.75" style="14" customWidth="1"/>
     <col min="3" max="7" width="9" style="14"/>
     <col min="8" max="8" width="20" style="14" customWidth="1"/>
@@ -1715,24 +1730,24 @@
         <v>18</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="16"/>
+        <v>19</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>20</v>
+      </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="16" t="s">
-        <v>19</v>
-      </c>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" s="14" customFormat="1" spans="1:9">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -1749,7 +1764,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -1758,40 +1773,46 @@
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" s="14" customFormat="1" spans="1:9">
+      <c r="A11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" s="14" customFormat="1" spans="1:9">
-      <c r="A12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" s="14" customFormat="1" spans="1:9">
-      <c r="A13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" s="14" customFormat="1" spans="1:9">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" s="14" customFormat="1" spans="1:9">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
@@ -1801,9 +1822,7 @@
       <c r="I14" s="18"/>
     </row>
     <row r="15" s="14" customFormat="1" spans="1:9">
-      <c r="A15" s="19" t="s">
-        <v>27</v>
-      </c>
+      <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -1814,15 +1833,11 @@
       <c r="I15" s="18"/>
     </row>
     <row r="16" s="14" customFormat="1" spans="1:9">
-      <c r="A16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A16" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
@@ -1831,9 +1846,13 @@
       <c r="I16" s="18"/>
     </row>
     <row r="17" s="14" customFormat="1" spans="1:9">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="4"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
@@ -1842,9 +1861,7 @@
       <c r="I17" s="18"/>
     </row>
     <row r="18" s="14" customFormat="1" spans="1:9">
-      <c r="A18" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="A18" s="18"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -1855,13 +1872,11 @@
       <c r="I18" s="18"/>
     </row>
     <row r="19" s="14" customFormat="1" spans="1:9">
-      <c r="A19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4"/>
+      <c r="A19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
@@ -1870,9 +1885,13 @@
       <c r="I19" s="18"/>
     </row>
     <row r="20" s="14" customFormat="1" spans="1:9">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
@@ -1881,11 +1900,13 @@
       <c r="I20" s="18"/>
     </row>
     <row r="21" s="14" customFormat="1" spans="1:9">
-      <c r="A21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
+      <c r="A21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="4"/>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
@@ -1894,69 +1915,110 @@
       <c r="I21" s="18"/>
     </row>
     <row r="22" s="14" customFormat="1" spans="1:9">
-      <c r="A22" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="A22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="B22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+    </row>
+    <row r="23" s="14" customFormat="1" spans="1:9">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+    </row>
+    <row r="24" s="14" customFormat="1" spans="1:9">
+      <c r="A24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+    </row>
+    <row r="25" s="14" customFormat="1" spans="1:9">
+      <c r="A25" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="B25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" s="14" customFormat="1" spans="1:9">
-      <c r="A23" s="12" t="s">
+      <c r="E25" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="F25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="12" t="s">
+      <c r="G25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" s="14" customFormat="1" spans="1:9">
-      <c r="A24" s="16" t="s">
+      <c r="H25" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="I25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16" t="s">
+    </row>
+    <row r="26" s="14" customFormat="1" spans="1:9">
+      <c r="A26" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24" s="16"/>
+      <c r="B26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" s="14" customFormat="1" spans="1:9">
+      <c r="A27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1969,7 +2031,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="30.8333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="29.8333333333333" style="1" customWidth="1"/>
@@ -2012,7 +2074,7 @@
     </row>
     <row r="2" s="1" customFormat="1" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -2021,15 +2083,15 @@
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -2041,21 +2103,21 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>13</v>
@@ -2067,18 +2129,18 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>13</v>
@@ -2090,18 +2152,18 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>13</v>
@@ -2113,18 +2175,18 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>13</v>
@@ -2136,18 +2198,18 @@
         <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>13</v>
@@ -2159,18 +2221,18 @@
         <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
@@ -2182,18 +2244,18 @@
         <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -2205,18 +2267,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -2228,18 +2290,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -2251,18 +2313,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
@@ -2274,18 +2336,18 @@
         <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
@@ -2297,18 +2359,18 @@
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
@@ -2320,18 +2382,18 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>13</v>
@@ -2343,18 +2405,18 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>13</v>
@@ -2366,18 +2428,18 @@
         <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>13</v>
@@ -2389,18 +2451,18 @@
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>13</v>
@@ -2412,18 +2474,18 @@
         <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>13</v>
@@ -2435,18 +2497,18 @@
         <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>13</v>
@@ -2458,18 +2520,18 @@
         <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>13</v>
@@ -2481,18 +2543,18 @@
         <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>13</v>
@@ -2504,18 +2566,18 @@
         <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>13</v>
@@ -2527,18 +2589,18 @@
         <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>13</v>
@@ -2550,18 +2612,18 @@
         <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>13</v>
@@ -2573,18 +2635,18 @@
         <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>13</v>
@@ -2596,18 +2658,18 @@
         <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>13</v>
@@ -2619,18 +2681,18 @@
         <v>11</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>13</v>
@@ -2642,18 +2704,18 @@
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>13</v>
@@ -2665,18 +2727,18 @@
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>13</v>
@@ -2688,18 +2750,18 @@
         <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>13</v>
@@ -2711,18 +2773,18 @@
         <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>13</v>
@@ -2734,18 +2796,18 @@
         <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>13</v>
@@ -2757,18 +2819,18 @@
         <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>13</v>
@@ -2780,18 +2842,18 @@
         <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>13</v>
@@ -2803,18 +2865,18 @@
         <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>13</v>
@@ -2826,18 +2888,18 @@
         <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>13</v>
@@ -2849,18 +2911,18 @@
         <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>13</v>
@@ -2872,18 +2934,18 @@
         <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>13</v>
@@ -2895,18 +2957,18 @@
         <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>13</v>
@@ -2918,18 +2980,18 @@
         <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>13</v>
@@ -2941,18 +3003,18 @@
         <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>13</v>
@@ -2964,18 +3026,18 @@
         <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>13</v>
@@ -2987,18 +3049,18 @@
         <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>13</v>
@@ -3010,18 +3072,18 @@
         <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>13</v>
@@ -3033,18 +3095,18 @@
         <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>13</v>
@@ -3056,18 +3118,18 @@
         <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>13</v>
@@ -3079,18 +3141,18 @@
         <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>13</v>
@@ -3102,41 +3164,41 @@
         <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:10">
       <c r="A50" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:10">
       <c r="A51" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>13</v>
@@ -3148,15 +3210,15 @@
         <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:10">
       <c r="A53" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -3170,13 +3232,13 @@
     </row>
     <row r="54" s="1" customFormat="1" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -3200,7 +3262,7 @@
     </row>
     <row r="56" s="1" customFormat="1" spans="1:10">
       <c r="A56" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3214,16 +3276,16 @@
     </row>
     <row r="57" s="1" customFormat="1" spans="1:10">
       <c r="A57" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
@@ -3246,7 +3308,7 @@
     </row>
     <row r="59" s="1" customFormat="1" spans="1:10">
       <c r="A59" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3260,10 +3322,10 @@
     </row>
     <row r="60" s="1" customFormat="1" spans="1:10">
       <c r="A60" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
@@ -3276,13 +3338,13 @@
     </row>
     <row r="61" s="1" customFormat="1" spans="1:10">
       <c r="A61" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -3306,7 +3368,7 @@
     </row>
     <row r="63" s="1" customFormat="1" spans="1:10">
       <c r="A63" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -3318,43 +3380,43 @@
     </row>
     <row r="64" s="1" customFormat="1" spans="1:10">
       <c r="A64" s="10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:8">
       <c r="A65" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C65" s="12"/>
       <c r="E65" s="13" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>

--- a/tool/cmd/gen-go-db/test.xlsx
+++ b/tool/cmd/gen-go-db/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8724"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="tm_teacher" sheetId="1" r:id="rId1"/>
@@ -126,10 +126,10 @@
     <t>tm_teacher_name_IDX</t>
   </si>
   <si>
+    <t>tm_teacher_phone_IDX</t>
+  </si>
+  <si>
     <t>索引</t>
-  </si>
-  <si>
-    <t>tm_teacher_phone_IDX</t>
   </si>
   <si>
     <t>tm_teacher_classid_IDX</t>
@@ -1570,7 +1570,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="27" style="14" customWidth="1"/>
     <col min="2" max="2" width="16.75" style="14" customWidth="1"/>
@@ -1861,9 +1861,13 @@
       <c r="I17" s="18"/>
     </row>
     <row r="18" s="14" customFormat="1" spans="1:9">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
@@ -1872,9 +1876,7 @@
       <c r="I18" s="18"/>
     </row>
     <row r="19" s="14" customFormat="1" spans="1:9">
-      <c r="A19" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="A19" s="18"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -1885,13 +1887,11 @@
       <c r="I19" s="18"/>
     </row>
     <row r="20" s="14" customFormat="1" spans="1:9">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
@@ -2031,7 +2031,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30.8333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="29.8333333333333" style="1" customWidth="1"/>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="59" s="1" customFormat="1" spans="1:10">
       <c r="A59" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
